--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Aggregated_normality.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Aggregated_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -470,16 +482,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C2" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9949537515640259</v>
+        <v>0.9949518442153931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01417193096131086</v>
+        <v>0.0179047416895628</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -487,10 +499,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9919743537902832</v>
+        <v>0.983501672744751</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006156301242299378</v>
+        <v>1.512980588813662e-06</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -505,16 +517,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C3" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9860791563987732</v>
+        <v>0.9863333702087402</v>
       </c>
       <c r="E3" t="n">
-        <v>1.466450953557796e-06</v>
+        <v>2.924222599176574e-06</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -522,10 +534,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9891359210014343</v>
+        <v>0.9924980998039246</v>
       </c>
       <c r="H3" t="n">
-        <v>3.575368100428022e-05</v>
+        <v>0.002933863783255219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -540,16 +552,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9896703362464905</v>
+        <v>0.9894532561302185</v>
       </c>
       <c r="E4" t="n">
-        <v>3.983379428973421e-05</v>
+        <v>4.833449929719791e-05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -557,10 +569,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9940211176872253</v>
+        <v>0.9879246354103088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005995623301714659</v>
+        <v>4.593719859258272e-05</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -575,16 +587,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>720</v>
+        <v>630</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9714980125427246</v>
+        <v>0.9709187150001526</v>
       </c>
       <c r="E5" t="n">
-        <v>6.427287868593368e-11</v>
+        <v>9.069749118406634e-11</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,10 +604,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9709203243255615</v>
+        <v>0.9706217050552368</v>
       </c>
       <c r="H5" t="n">
-        <v>9.077570639615118e-11</v>
+        <v>6.382037120999939e-10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
